--- a/Диздок (GDD)/Баланс.xlsx
+++ b/Диздок (GDD)/Баланс.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Working folder of Dima\Projects\Gearspell Tower\Диздок (GDD)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBFD810-5099-4FE1-A26B-019D1C6CBF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75DA914-843C-4FD9-A39E-2FC013CA5F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,12 +514,6 @@
     <t>рабочий/бот</t>
   </si>
   <si>
-    <t>огонь/свет элементали</t>
-  </si>
-  <si>
-    <t>каменно-стеклянный магич. Элементаль</t>
-  </si>
-  <si>
     <t>автоматон</t>
   </si>
   <si>
@@ -610,27 +604,18 @@
     <t>бехолдер</t>
   </si>
   <si>
-    <t>охотник с мантией</t>
-  </si>
-  <si>
     <t>легкий/обычный</t>
   </si>
   <si>
     <t>асассин</t>
   </si>
   <si>
-    <t>спрут</t>
-  </si>
-  <si>
     <t>акробат</t>
   </si>
   <si>
     <t>перемещается рывками</t>
   </si>
   <si>
-    <t>робот</t>
-  </si>
-  <si>
     <t>тяжелый</t>
   </si>
   <si>
@@ -758,6 +743,21 @@
   </si>
   <si>
     <t>невосприимчив к звуку</t>
+  </si>
+  <si>
+    <t>рунный элементаль</t>
+  </si>
+  <si>
+    <t>огн. элементаль</t>
+  </si>
+  <si>
+    <t>спрут-техник</t>
+  </si>
+  <si>
+    <t>охотник в мантии</t>
+  </si>
+  <si>
+    <t>робот-берсерк</t>
   </si>
 </sst>
 </file>
@@ -1164,9 +1164,60 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1174,57 +1225,18 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1233,35 +1245,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1564,15 +1564,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="66"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="70"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
@@ -1598,15 +1598,15 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="67">
+      <c r="A3" s="64">
         <v>1</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="76"/>
+      <c r="C3" s="57"/>
       <c r="D3" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E3" s="73" t="s">
         <v>18</v>
@@ -1619,67 +1619,67 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="76"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="57"/>
       <c r="D4" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E4" s="73"/>
       <c r="F4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="76" t="s">
+      <c r="G4" s="57" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="67"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="76"/>
+      <c r="A5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="57"/>
       <c r="D5" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E5" s="73"/>
       <c r="F5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="76"/>
+      <c r="G5" s="57"/>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="67"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="76"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="57"/>
       <c r="D6" s="4"/>
       <c r="E6" s="73"/>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="76"/>
+      <c r="G6" s="57"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="76"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="4"/>
       <c r="E7" s="73"/>
       <c r="F7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="76"/>
+      <c r="G7" s="57"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="68">
+      <c r="A8" s="65">
         <v>2</v>
       </c>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="74"/>
+      <c r="C8" s="58"/>
       <c r="D8" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="74" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="58" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="10" t="s">
@@ -1690,13 +1690,13 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="68"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="74"/>
+      <c r="A9" s="65"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="58"/>
       <c r="D9" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="74"/>
+        <v>128</v>
+      </c>
+      <c r="E9" s="58"/>
       <c r="F9" s="10" t="s">
         <v>24</v>
       </c>
@@ -1705,54 +1705,54 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="68"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="74"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="58"/>
       <c r="D10" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" s="74"/>
+        <v>125</v>
+      </c>
+      <c r="E10" s="58"/>
       <c r="F10" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="68"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="74"/>
+      <c r="A11" s="65"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="58"/>
       <c r="D11" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="74"/>
+        <v>129</v>
+      </c>
+      <c r="E11" s="58"/>
       <c r="F11" s="12" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="68"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="74"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="74"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="11" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="69">
+      <c r="A13" s="66">
         <v>3</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="75"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" s="75" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="59" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="25" t="s">
@@ -1763,13 +1763,13 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="69"/>
-      <c r="B14" s="69"/>
-      <c r="C14" s="75"/>
+      <c r="A14" s="66"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" s="75"/>
+        <v>131</v>
+      </c>
+      <c r="E14" s="59"/>
       <c r="F14" s="25" t="s">
         <v>34</v>
       </c>
@@ -1778,52 +1778,52 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="69"/>
-      <c r="B15" s="69"/>
-      <c r="C15" s="75"/>
+      <c r="A15" s="66"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="59"/>
       <c r="D15" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" s="75"/>
+        <v>130</v>
+      </c>
+      <c r="E15" s="59"/>
       <c r="F15" s="27" t="s">
         <v>35</v>
       </c>
       <c r="G15" s="72"/>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="69"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="75"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="75"/>
+        <v>133</v>
+      </c>
+      <c r="E16" s="59"/>
       <c r="F16" s="28" t="s">
         <v>36</v>
       </c>
       <c r="G16" s="72"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="69"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="75"/>
+      <c r="A17" s="66"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="13"/>
-      <c r="E17" s="75"/>
+      <c r="E17" s="59"/>
       <c r="F17" s="27" t="s">
         <v>4</v>
       </c>
       <c r="G17" s="72"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="70">
+      <c r="A18" s="67">
         <v>4</v>
       </c>
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="67" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="60"/>
       <c r="D18" s="14" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E18" s="60" t="s">
         <v>17</v>
@@ -1836,11 +1836,11 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="70"/>
-      <c r="B19" s="70"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="60"/>
       <c r="D19" s="14" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E19" s="60"/>
       <c r="F19" s="29" t="s">
@@ -1851,11 +1851,11 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="70"/>
-      <c r="B20" s="70"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="60"/>
       <c r="D20" s="14" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E20" s="60"/>
       <c r="F20" s="30" t="s">
@@ -1864,11 +1864,11 @@
       <c r="G20" s="60"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="70"/>
-      <c r="B21" s="70"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="60"/>
       <c r="D21" s="14" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E21" s="60"/>
       <c r="F21" s="31" t="s">
@@ -1877,8 +1877,8 @@
       <c r="G21" s="60"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="70"/>
-      <c r="B22" s="70"/>
+      <c r="A22" s="67"/>
+      <c r="B22" s="67"/>
       <c r="C22" s="60"/>
       <c r="D22" s="14"/>
       <c r="E22" s="60"/>
@@ -1888,15 +1888,15 @@
       <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="56">
+      <c r="A23" s="68">
         <v>5</v>
       </c>
-      <c r="B23" s="56" t="s">
+      <c r="B23" s="68" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="61"/>
       <c r="D23" s="15" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E23" s="61" t="s">
         <v>19</v>
@@ -1909,11 +1909,11 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="56"/>
-      <c r="B24" s="56"/>
+      <c r="A24" s="68"/>
+      <c r="B24" s="68"/>
       <c r="C24" s="61"/>
       <c r="D24" s="15" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E24" s="61"/>
       <c r="F24" s="32" t="s">
@@ -1924,11 +1924,11 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="56"/>
-      <c r="B25" s="56"/>
+      <c r="A25" s="68"/>
+      <c r="B25" s="68"/>
       <c r="C25" s="61"/>
       <c r="D25" s="15" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E25" s="61"/>
       <c r="F25" s="33" t="s">
@@ -1937,11 +1937,11 @@
       <c r="G25" s="61"/>
     </row>
     <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="56"/>
-      <c r="B26" s="56"/>
+      <c r="A26" s="68"/>
+      <c r="B26" s="68"/>
       <c r="C26" s="61"/>
       <c r="D26" s="15" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E26" s="61"/>
       <c r="F26" s="34" t="s">
@@ -1950,8 +1950,8 @@
       <c r="G26" s="61"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="56"/>
-      <c r="B27" s="56"/>
+      <c r="A27" s="68"/>
+      <c r="B27" s="68"/>
       <c r="C27" s="61"/>
       <c r="D27" s="15"/>
       <c r="E27" s="61"/>
@@ -1961,15 +1961,15 @@
       <c r="G27" s="61"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="57">
+      <c r="A28" s="74">
         <v>6</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="62"/>
       <c r="D28" s="16" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E28" s="62" t="s">
         <v>20</v>
@@ -1982,11 +1982,11 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="57"/>
-      <c r="B29" s="57"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="74"/>
       <c r="C29" s="62"/>
       <c r="D29" s="16" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E29" s="62"/>
       <c r="F29" s="35" t="s">
@@ -1997,11 +1997,11 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="57"/>
-      <c r="B30" s="57"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="74"/>
       <c r="C30" s="62"/>
       <c r="D30" s="16" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E30" s="62"/>
       <c r="F30" s="36" t="s">
@@ -2010,8 +2010,8 @@
       <c r="G30" s="62"/>
     </row>
     <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="57"/>
-      <c r="B31" s="57"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="74"/>
       <c r="C31" s="62"/>
       <c r="D31" s="16"/>
       <c r="E31" s="62"/>
@@ -2021,8 +2021,8 @@
       <c r="G31" s="62"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="57"/>
-      <c r="B32" s="57"/>
+      <c r="A32" s="74"/>
+      <c r="B32" s="74"/>
       <c r="C32" s="62"/>
       <c r="D32" s="16"/>
       <c r="E32" s="62"/>
@@ -2032,15 +2032,15 @@
       <c r="G32" s="62"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="58">
+      <c r="A33" s="75">
         <v>7</v>
       </c>
-      <c r="B33" s="58" t="s">
+      <c r="B33" s="75" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="63"/>
       <c r="D33" s="17" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E33" s="63" t="s">
         <v>21</v>
@@ -2051,11 +2051,11 @@
       <c r="G33" s="22"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="58"/>
-      <c r="B34" s="58"/>
+      <c r="A34" s="75"/>
+      <c r="B34" s="75"/>
       <c r="C34" s="63"/>
       <c r="D34" s="17" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E34" s="63"/>
       <c r="F34" s="38" t="s">
@@ -2064,11 +2064,11 @@
       <c r="G34" s="63"/>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
+      <c r="A35" s="75"/>
+      <c r="B35" s="75"/>
       <c r="C35" s="63"/>
       <c r="D35" s="17" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E35" s="63"/>
       <c r="F35" s="39" t="s">
@@ -2077,8 +2077,8 @@
       <c r="G35" s="63"/>
     </row>
     <row r="36" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="58"/>
-      <c r="B36" s="58"/>
+      <c r="A36" s="75"/>
+      <c r="B36" s="75"/>
       <c r="C36" s="63"/>
       <c r="D36" s="17"/>
       <c r="E36" s="63"/>
@@ -2088,8 +2088,8 @@
       <c r="G36" s="63"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="58"/>
-      <c r="B37" s="58"/>
+      <c r="A37" s="75"/>
+      <c r="B37" s="75"/>
       <c r="C37" s="63"/>
       <c r="D37" s="17"/>
       <c r="E37" s="63"/>
@@ -2099,17 +2099,17 @@
       <c r="G37" s="63"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="59">
+      <c r="A38" s="56">
         <v>8</v>
       </c>
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="64"/>
+      <c r="C38" s="76"/>
       <c r="D38" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="E38" s="64" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="76" t="s">
         <v>22</v>
       </c>
       <c r="F38" s="41" t="s">
@@ -2120,82 +2120,57 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="59"/>
-      <c r="B39" s="59"/>
-      <c r="C39" s="64"/>
+      <c r="A39" s="56"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="76"/>
       <c r="D39" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="E39" s="64"/>
+        <v>146</v>
+      </c>
+      <c r="E39" s="76"/>
       <c r="F39" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="G39" s="64" t="s">
+      <c r="G39" s="76" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="59"/>
-      <c r="B40" s="59"/>
-      <c r="C40" s="64"/>
+      <c r="A40" s="56"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="76"/>
       <c r="D40" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="E40" s="64"/>
+        <v>147</v>
+      </c>
+      <c r="E40" s="76"/>
       <c r="F40" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="64"/>
+      <c r="G40" s="76"/>
     </row>
     <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="59"/>
-      <c r="B41" s="59"/>
-      <c r="C41" s="64"/>
+      <c r="A41" s="56"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="76"/>
       <c r="D41" s="18"/>
-      <c r="E41" s="64"/>
+      <c r="E41" s="76"/>
       <c r="F41" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="G41" s="64"/>
+      <c r="G41" s="76"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="59"/>
-      <c r="B42" s="59"/>
-      <c r="C42" s="64"/>
+      <c r="A42" s="56"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="76"/>
       <c r="D42" s="18"/>
-      <c r="E42" s="64"/>
+      <c r="E42" s="76"/>
       <c r="F42" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G42" s="64"/>
+      <c r="G42" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="B38:B42"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="C18:C22"/>
-    <mergeCell ref="C23:C27"/>
-    <mergeCell ref="C28:C32"/>
-    <mergeCell ref="C33:C37"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="G9:G12"/>
-    <mergeCell ref="G14:G17"/>
-    <mergeCell ref="E3:E7"/>
-    <mergeCell ref="E8:E12"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="E18:E22"/>
-    <mergeCell ref="G4:G7"/>
     <mergeCell ref="A23:A27"/>
     <mergeCell ref="A28:A32"/>
     <mergeCell ref="A33:A37"/>
@@ -2212,6 +2187,31 @@
     <mergeCell ref="E38:E42"/>
     <mergeCell ref="B28:B32"/>
     <mergeCell ref="B33:B37"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="E18:E22"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="B38:B42"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="C28:C32"/>
+    <mergeCell ref="C33:C37"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="B23:B27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2232,15 +2232,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
@@ -2252,10 +2252,10 @@
       <c r="C2" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="80"/>
+      <c r="E2" s="88"/>
       <c r="F2" s="3" t="s">
         <v>70</v>
       </c>
@@ -2264,871 +2264,813 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="87">
+      <c r="A3" s="77">
         <v>1</v>
       </c>
-      <c r="B3" s="83" t="s">
-        <v>74</v>
+      <c r="B3" s="79" t="s">
+        <v>152</v>
       </c>
       <c r="C3" s="53" t="s">
         <v>72</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3" s="50">
         <v>6</v>
       </c>
       <c r="F3" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="G3" s="82"/>
+        <v>110</v>
+      </c>
+      <c r="G3" s="86"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="87"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="81" t="s">
-        <v>101</v>
+      <c r="A4" s="77"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80" t="s">
+        <v>99</v>
       </c>
       <c r="D4" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E4" s="50">
         <v>5</v>
       </c>
       <c r="F4" s="45"/>
-      <c r="G4" s="82"/>
+      <c r="G4" s="86"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="87"/>
-      <c r="B5" s="83"/>
-      <c r="C5" s="81"/>
+      <c r="A5" s="77"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
       <c r="D5" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" s="50">
         <v>2.5</v>
       </c>
       <c r="F5" s="45"/>
-      <c r="G5" s="82"/>
+      <c r="G5" s="86"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="87">
+      <c r="A6" s="77">
         <v>2</v>
       </c>
-      <c r="B6" s="83" t="s">
-        <v>75</v>
+      <c r="B6" s="79" t="s">
+        <v>151</v>
       </c>
       <c r="C6" s="54" t="s">
         <v>72</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E6" s="51">
         <v>10</v>
       </c>
       <c r="F6" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="86"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="77"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="80" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="49" t="s">
         <v>81</v>
-      </c>
-      <c r="G6" s="82"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="87"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>83</v>
       </c>
       <c r="E7" s="51">
         <v>10</v>
       </c>
       <c r="F7" s="45"/>
-      <c r="G7" s="82"/>
+      <c r="G7" s="86"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="87"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="81"/>
+      <c r="A8" s="77"/>
+      <c r="B8" s="79"/>
+      <c r="C8" s="80"/>
       <c r="D8" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E8" s="51">
         <v>1.8</v>
       </c>
       <c r="F8" s="45"/>
-      <c r="G8" s="82"/>
+      <c r="G8" s="86"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="87">
+      <c r="A9" s="77">
         <v>3</v>
       </c>
-      <c r="B9" s="83" t="s">
-        <v>76</v>
+      <c r="B9" s="79" t="s">
+        <v>74</v>
       </c>
       <c r="C9" s="55" t="s">
         <v>73</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E9" s="51"/>
       <c r="F9" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="G9" s="82"/>
+        <v>150</v>
+      </c>
+      <c r="G9" s="86"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="87"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="81" t="s">
-        <v>107</v>
+      <c r="A10" s="77"/>
+      <c r="B10" s="79"/>
+      <c r="C10" s="80" t="s">
+        <v>104</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E10" s="51"/>
       <c r="F10" s="45"/>
-      <c r="G10" s="82"/>
+      <c r="G10" s="86"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="87"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="81"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="80"/>
       <c r="D11" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E11" s="51"/>
       <c r="F11" s="45"/>
-      <c r="G11" s="82"/>
+      <c r="G11" s="86"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="87">
+      <c r="A12" s="77">
         <v>4</v>
       </c>
-      <c r="B12" s="83" t="s">
-        <v>77</v>
+      <c r="B12" s="79" t="s">
+        <v>75</v>
       </c>
       <c r="C12" s="55" t="s">
         <v>73</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E12" s="51"/>
       <c r="F12" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="82"/>
+        <v>78</v>
+      </c>
+      <c r="G12" s="86"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="87"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="81" t="s">
-        <v>79</v>
+      <c r="A13" s="77"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="80" t="s">
+        <v>77</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E13" s="51"/>
       <c r="F13" s="45"/>
-      <c r="G13" s="82"/>
+      <c r="G13" s="86"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="87"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="81"/>
+      <c r="A14" s="77"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="80"/>
       <c r="D14" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E14" s="51"/>
       <c r="F14" s="45"/>
-      <c r="G14" s="82"/>
+      <c r="G14" s="86"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="87">
+      <c r="A15" s="77">
         <v>5</v>
       </c>
-      <c r="B15" s="83" t="s">
-        <v>103</v>
+      <c r="B15" s="79" t="s">
+        <v>101</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E15" s="51"/>
       <c r="F15" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="G15" s="82"/>
+        <v>123</v>
+      </c>
+      <c r="G15" s="86"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="87"/>
-      <c r="B16" s="83"/>
-      <c r="C16" s="77" t="s">
-        <v>102</v>
+      <c r="A16" s="77"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="81" t="s">
+        <v>100</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E16" s="51"/>
       <c r="F16" s="45"/>
-      <c r="G16" s="82"/>
+      <c r="G16" s="86"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="87"/>
-      <c r="B17" s="83"/>
-      <c r="C17" s="78"/>
+      <c r="A17" s="77"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="82"/>
       <c r="D17" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E17" s="51"/>
       <c r="F17" s="45"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="86"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="87">
+      <c r="A18" s="77">
         <v>6</v>
       </c>
-      <c r="B18" s="83" t="s">
-        <v>108</v>
+      <c r="B18" s="79" t="s">
+        <v>105</v>
       </c>
       <c r="C18" s="53" t="s">
         <v>73</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E18" s="51"/>
       <c r="F18" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="G18" s="82"/>
+        <v>122</v>
+      </c>
+      <c r="G18" s="86"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="87"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="77" t="s">
-        <v>102</v>
+      <c r="A19" s="77"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="81" t="s">
+        <v>100</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E19" s="51"/>
       <c r="F19" s="45"/>
-      <c r="G19" s="82"/>
+      <c r="G19" s="86"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="87"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="78"/>
+      <c r="A20" s="77"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="82"/>
       <c r="D20" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E20" s="51"/>
       <c r="F20" s="45"/>
-      <c r="G20" s="82"/>
+      <c r="G20" s="86"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="87">
+      <c r="A21" s="77">
         <v>7</v>
       </c>
-      <c r="B21" s="83" t="s">
-        <v>109</v>
+      <c r="B21" s="79" t="s">
+        <v>153</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E21" s="51"/>
       <c r="F21" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" s="82"/>
+        <v>78</v>
+      </c>
+      <c r="G21" s="86"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="87"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="77" t="s">
-        <v>102</v>
+      <c r="A22" s="77"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="81" t="s">
+        <v>100</v>
       </c>
       <c r="D22" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E22" s="51"/>
       <c r="F22" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G22" s="82"/>
+        <v>121</v>
+      </c>
+      <c r="G22" s="86"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="87"/>
-      <c r="B23" s="83"/>
-      <c r="C23" s="78"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="82"/>
       <c r="D23" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E23" s="51"/>
       <c r="F23" s="45"/>
-      <c r="G23" s="82"/>
+      <c r="G23" s="86"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="87">
+      <c r="A24" s="77">
         <v>8</v>
       </c>
-      <c r="B24" s="83" t="s">
-        <v>104</v>
+      <c r="B24" s="79" t="s">
+        <v>102</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E24" s="51"/>
       <c r="F24" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="G24" s="82"/>
+        <v>78</v>
+      </c>
+      <c r="G24" s="86"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="87"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="77" t="s">
-        <v>102</v>
+      <c r="A25" s="77"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="81" t="s">
+        <v>100</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E25" s="51"/>
       <c r="F25" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="G25" s="82"/>
+        <v>116</v>
+      </c>
+      <c r="G25" s="86"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="87"/>
-      <c r="B26" s="83"/>
-      <c r="C26" s="78"/>
+      <c r="A26" s="77"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="82"/>
       <c r="D26" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E26" s="51"/>
       <c r="F26" s="45"/>
-      <c r="G26" s="82"/>
+      <c r="G26" s="86"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="87">
+      <c r="A27" s="77">
         <v>9</v>
       </c>
-      <c r="B27" s="83" t="s">
-        <v>110</v>
+      <c r="B27" s="79" t="s">
+        <v>106</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E27" s="51"/>
       <c r="F27" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="82"/>
+        <v>107</v>
+      </c>
+      <c r="G27" s="86"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="87"/>
-      <c r="B28" s="83"/>
-      <c r="C28" s="77" t="s">
-        <v>102</v>
+      <c r="A28" s="77"/>
+      <c r="B28" s="79"/>
+      <c r="C28" s="81" t="s">
+        <v>100</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E28" s="51"/>
       <c r="F28" s="45"/>
-      <c r="G28" s="82"/>
+      <c r="G28" s="86"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="87"/>
-      <c r="B29" s="83"/>
-      <c r="C29" s="78"/>
+      <c r="A29" s="77"/>
+      <c r="B29" s="79"/>
+      <c r="C29" s="82"/>
       <c r="D29" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E29" s="51"/>
       <c r="F29" s="45"/>
-      <c r="G29" s="82"/>
+      <c r="G29" s="86"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="87">
+      <c r="A30" s="77">
         <v>10</v>
       </c>
-      <c r="B30" s="84" t="s">
-        <v>106</v>
+      <c r="B30" s="83" t="s">
+        <v>154</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E30" s="51"/>
       <c r="F30" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="G30" s="82"/>
+        <v>119</v>
+      </c>
+      <c r="G30" s="86"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="87"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="77" t="s">
-        <v>102</v>
+      <c r="A31" s="77"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="81" t="s">
+        <v>100</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E31" s="51"/>
       <c r="F31" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="G31" s="82"/>
+        <v>120</v>
+      </c>
+      <c r="G31" s="86"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="87"/>
-      <c r="B32" s="86"/>
-      <c r="C32" s="78"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="82"/>
       <c r="D32" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E32" s="51"/>
       <c r="F32" s="45"/>
-      <c r="G32" s="82"/>
+      <c r="G32" s="86"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="87">
+      <c r="A33" s="77">
         <v>11</v>
       </c>
-      <c r="B33" s="83" t="s">
-        <v>112</v>
+      <c r="B33" s="79" t="s">
+        <v>155</v>
       </c>
       <c r="C33" s="53" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E33" s="51"/>
       <c r="F33" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="G33" s="82"/>
+        <v>148</v>
+      </c>
+      <c r="G33" s="86"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="87"/>
-      <c r="B34" s="83"/>
-      <c r="C34" s="77" t="s">
-        <v>102</v>
+      <c r="A34" s="77"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="81" t="s">
+        <v>100</v>
       </c>
       <c r="D34" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E34" s="51"/>
       <c r="F34" s="45"/>
-      <c r="G34" s="82"/>
+      <c r="G34" s="86"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="87"/>
-      <c r="B35" s="83"/>
-      <c r="C35" s="78"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="82"/>
       <c r="D35" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E35" s="51"/>
       <c r="F35" s="45"/>
-      <c r="G35" s="82"/>
+      <c r="G35" s="86"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="87">
+      <c r="A36" s="77">
         <v>12</v>
       </c>
-      <c r="B36" s="83" t="s">
-        <v>114</v>
+      <c r="B36" s="79" t="s">
+        <v>109</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E36" s="51"/>
       <c r="F36" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="G36" s="82"/>
+        <v>117</v>
+      </c>
+      <c r="G36" s="86"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="87"/>
-      <c r="B37" s="83"/>
-      <c r="C37" s="77" t="s">
-        <v>113</v>
+      <c r="A37" s="77"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="81" t="s">
+        <v>108</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E37" s="51"/>
       <c r="F37" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="G37" s="82"/>
+        <v>116</v>
+      </c>
+      <c r="G37" s="86"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="87"/>
-      <c r="B38" s="83"/>
-      <c r="C38" s="78"/>
+      <c r="A38" s="77"/>
+      <c r="B38" s="79"/>
+      <c r="C38" s="82"/>
       <c r="D38" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E38" s="51"/>
       <c r="F38" s="45"/>
-      <c r="G38" s="82"/>
+      <c r="G38" s="86"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="87">
+      <c r="A39" s="77">
         <v>13</v>
       </c>
-      <c r="B39" s="83" t="s">
-        <v>105</v>
+      <c r="B39" s="79" t="s">
+        <v>103</v>
       </c>
       <c r="C39" s="53" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E39" s="51"/>
       <c r="F39" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="G39" s="82"/>
+        <v>114</v>
+      </c>
+      <c r="G39" s="86"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="87"/>
-      <c r="B40" s="83"/>
-      <c r="C40" s="77" t="s">
-        <v>113</v>
+      <c r="A40" s="77"/>
+      <c r="B40" s="79"/>
+      <c r="C40" s="81" t="s">
+        <v>108</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E40" s="51"/>
       <c r="F40" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="G40" s="82"/>
+        <v>115</v>
+      </c>
+      <c r="G40" s="86"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="87"/>
-      <c r="B41" s="83"/>
-      <c r="C41" s="78"/>
+      <c r="A41" s="77"/>
+      <c r="B41" s="79"/>
+      <c r="C41" s="82"/>
       <c r="D41" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E41" s="51"/>
       <c r="F41" s="45"/>
-      <c r="G41" s="82"/>
+      <c r="G41" s="86"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="87">
+      <c r="A42" s="77">
         <v>14</v>
       </c>
-      <c r="B42" s="83" t="s">
-        <v>95</v>
+      <c r="B42" s="79" t="s">
+        <v>93</v>
       </c>
       <c r="C42" s="53" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E42" s="51"/>
       <c r="F42" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="G42" s="82"/>
+        <v>113</v>
+      </c>
+      <c r="G42" s="86"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="87"/>
-      <c r="B43" s="83"/>
-      <c r="C43" s="77" t="s">
-        <v>96</v>
+      <c r="A43" s="77"/>
+      <c r="B43" s="79"/>
+      <c r="C43" s="81" t="s">
+        <v>94</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E43" s="51"/>
       <c r="F43" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="G43" s="82"/>
+        <v>118</v>
+      </c>
+      <c r="G43" s="86"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="87"/>
-      <c r="B44" s="83"/>
-      <c r="C44" s="78"/>
+      <c r="A44" s="77"/>
+      <c r="B44" s="79"/>
+      <c r="C44" s="82"/>
       <c r="D44" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E44" s="51"/>
       <c r="F44" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="G44" s="82"/>
+        <v>149</v>
+      </c>
+      <c r="G44" s="86"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="87">
+      <c r="A45" s="77">
         <v>15</v>
       </c>
-      <c r="B45" s="83" t="s">
-        <v>94</v>
+      <c r="B45" s="79" t="s">
+        <v>92</v>
       </c>
       <c r="C45" s="53" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E45" s="51"/>
       <c r="F45" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45" s="82"/>
+        <v>98</v>
+      </c>
+      <c r="G45" s="86"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="87"/>
-      <c r="B46" s="83"/>
-      <c r="C46" s="77" t="s">
-        <v>96</v>
+      <c r="A46" s="77"/>
+      <c r="B46" s="79"/>
+      <c r="C46" s="81" t="s">
+        <v>94</v>
       </c>
       <c r="D46" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E46" s="51"/>
       <c r="F46" s="45"/>
-      <c r="G46" s="82"/>
+      <c r="G46" s="86"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="87"/>
-      <c r="B47" s="83"/>
-      <c r="C47" s="78"/>
+      <c r="A47" s="77"/>
+      <c r="B47" s="79"/>
+      <c r="C47" s="82"/>
       <c r="D47" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E47" s="51"/>
       <c r="F47" s="45"/>
-      <c r="G47" s="82"/>
+      <c r="G47" s="86"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="87">
+      <c r="A48" s="77">
         <v>16</v>
       </c>
-      <c r="B48" s="83" t="s">
-        <v>93</v>
+      <c r="B48" s="79" t="s">
+        <v>91</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E48" s="51"/>
       <c r="F48" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="G48" s="82"/>
+        <v>111</v>
+      </c>
+      <c r="G48" s="86"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="87"/>
-      <c r="B49" s="83"/>
-      <c r="C49" s="77" t="s">
-        <v>96</v>
+      <c r="A49" s="77"/>
+      <c r="B49" s="79"/>
+      <c r="C49" s="81" t="s">
+        <v>94</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E49" s="51">
         <v>0</v>
       </c>
       <c r="F49" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="G49" s="82"/>
+        <v>97</v>
+      </c>
+      <c r="G49" s="86"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="87"/>
-      <c r="B50" s="83"/>
-      <c r="C50" s="78"/>
+      <c r="A50" s="77"/>
+      <c r="B50" s="79"/>
+      <c r="C50" s="82"/>
       <c r="D50" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E50" s="51"/>
       <c r="F50" s="45"/>
-      <c r="G50" s="82"/>
+      <c r="G50" s="86"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="87">
+      <c r="A51" s="77">
         <v>17</v>
       </c>
-      <c r="B51" s="83" t="s">
-        <v>92</v>
+      <c r="B51" s="79" t="s">
+        <v>90</v>
       </c>
       <c r="C51" s="53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E51" s="51"/>
       <c r="F51" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="G51" s="82"/>
+        <v>112</v>
+      </c>
+      <c r="G51" s="86"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="87"/>
-      <c r="B52" s="83"/>
-      <c r="C52" s="77" t="s">
-        <v>96</v>
+      <c r="A52" s="77"/>
+      <c r="B52" s="79"/>
+      <c r="C52" s="81" t="s">
+        <v>94</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E52" s="51"/>
       <c r="F52" s="45"/>
-      <c r="G52" s="82"/>
+      <c r="G52" s="86"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="87"/>
-      <c r="B53" s="83"/>
-      <c r="C53" s="78"/>
+      <c r="A53" s="77"/>
+      <c r="B53" s="79"/>
+      <c r="C53" s="82"/>
       <c r="D53" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E53" s="51"/>
       <c r="F53" s="45"/>
-      <c r="G53" s="82"/>
+      <c r="G53" s="86"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="87">
+      <c r="A54" s="77">
         <v>18</v>
       </c>
-      <c r="B54" s="83" t="s">
-        <v>91</v>
+      <c r="B54" s="79" t="s">
+        <v>89</v>
       </c>
       <c r="C54" s="53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E54" s="51"/>
       <c r="F54" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G54" s="82"/>
+        <v>95</v>
+      </c>
+      <c r="G54" s="86"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="87"/>
-      <c r="B55" s="83"/>
-      <c r="C55" s="77" t="s">
-        <v>96</v>
+      <c r="A55" s="77"/>
+      <c r="B55" s="79"/>
+      <c r="C55" s="81" t="s">
+        <v>94</v>
       </c>
       <c r="D55" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E55" s="51"/>
       <c r="F55" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="G55" s="82"/>
+        <v>96</v>
+      </c>
+      <c r="G55" s="86"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="87"/>
-      <c r="B56" s="83"/>
-      <c r="C56" s="78"/>
+      <c r="A56" s="77"/>
+      <c r="B56" s="79"/>
+      <c r="C56" s="82"/>
       <c r="D56" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E56" s="51"/>
       <c r="F56" s="45"/>
-      <c r="G56" s="82"/>
+      <c r="G56" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="G48:G50"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="G54:G56"/>
     <mergeCell ref="C55:C56"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="C37:C38"/>
@@ -3145,6 +3087,64 @@
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Диздок (GDD)/Баланс.xlsx
+++ b/Диздок (GDD)/Баланс.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Working folder of Dima\Projects\Gearspell Tower\Диздок (GDD)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629C79D9-5BF1-4718-BE35-A03B7D139934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F76BE42-4ED7-4812-A6F7-C351C6C11F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Снаряжение" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="163">
   <si>
     <t>Название</t>
   </si>
@@ -776,6 +776,21 @@
   <si>
     <t>Ускоритель</t>
   </si>
+  <si>
+    <t>Drone</t>
+  </si>
+  <si>
+    <t>Mage</t>
+  </si>
+  <si>
+    <t>Fire_Elemental</t>
+  </si>
+  <si>
+    <t>Spider_Golem</t>
+  </si>
+  <si>
+    <t>Drop (ev)</t>
+  </si>
 </sst>
 </file>
 
@@ -784,12 +799,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1032,7 +1055,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1040,193 +1063,199 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1234,17 +1263,32 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1252,21 +1296,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1276,18 +1305,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1589,15 +1613,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="70"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
@@ -1623,17 +1647,17 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="65">
+      <c r="A3" s="64">
         <v>1</v>
       </c>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="74"/>
+      <c r="C3" s="57"/>
       <c r="D3" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="73" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -1644,67 +1668,67 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="74"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="57"/>
       <c r="D4" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="71"/>
+      <c r="E4" s="73"/>
       <c r="F4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="74" t="s">
+      <c r="G4" s="57" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="74"/>
+      <c r="A5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="57"/>
       <c r="D5" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E5" s="71"/>
+      <c r="E5" s="73"/>
       <c r="F5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="74"/>
+      <c r="G5" s="57"/>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="74"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="57"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="71"/>
+      <c r="E6" s="73"/>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="74"/>
+      <c r="G6" s="57"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="65"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="74"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="71"/>
+      <c r="E7" s="73"/>
       <c r="F7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="74"/>
+      <c r="G7" s="57"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="66">
+      <c r="A8" s="65">
         <v>2</v>
       </c>
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="72"/>
+      <c r="C8" s="58"/>
       <c r="D8" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="58" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="10" t="s">
@@ -1715,69 +1739,69 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="66"/>
-      <c r="B9" s="66"/>
-      <c r="C9" s="72"/>
+      <c r="A9" s="65"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="58"/>
       <c r="D9" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="72"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="69" t="s">
+      <c r="G9" s="71" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="66"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="72"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="58"/>
       <c r="D10" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="72"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="69"/>
+      <c r="G10" s="71"/>
     </row>
     <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="66"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="72"/>
+      <c r="A11" s="65"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="58"/>
       <c r="D11" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="72"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="69"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="66"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="72"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="72"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="69"/>
+      <c r="G12" s="71"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="67">
+      <c r="A13" s="66">
         <v>3</v>
       </c>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="73"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="73" t="s">
+      <c r="E13" s="59" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="24" t="s">
@@ -1788,69 +1812,69 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="67"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="73"/>
+      <c r="A14" s="66"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E14" s="73"/>
+      <c r="E14" s="59"/>
       <c r="F14" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="70" t="s">
+      <c r="G14" s="72" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="67"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="73"/>
+      <c r="A15" s="66"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="59"/>
       <c r="D15" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E15" s="73"/>
+      <c r="E15" s="59"/>
       <c r="F15" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="70"/>
+      <c r="G15" s="72"/>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="67"/>
-      <c r="B16" s="67"/>
-      <c r="C16" s="73"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E16" s="73"/>
+      <c r="E16" s="59"/>
       <c r="F16" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="70"/>
+      <c r="G16" s="72"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="67"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="73"/>
+      <c r="A17" s="66"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="13"/>
-      <c r="E17" s="73"/>
+      <c r="E17" s="59"/>
       <c r="F17" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G17" s="70"/>
+      <c r="G17" s="72"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="68">
+      <c r="A18" s="67">
         <v>4</v>
       </c>
-      <c r="B18" s="68" t="s">
+      <c r="B18" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="58"/>
+      <c r="C18" s="60"/>
       <c r="D18" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="60" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="28" t="s">
@@ -1861,69 +1885,69 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="68"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="58"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="60"/>
       <c r="D19" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E19" s="58"/>
+      <c r="E19" s="60"/>
       <c r="F19" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="58" t="s">
+      <c r="G19" s="60" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="68"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="58"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="60"/>
       <c r="D20" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E20" s="58"/>
+      <c r="E20" s="60"/>
       <c r="F20" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="G20" s="58"/>
+      <c r="G20" s="60"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="68"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="58"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E21" s="58"/>
+      <c r="E21" s="60"/>
       <c r="F21" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="58"/>
+      <c r="G21" s="60"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="68"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="58"/>
+      <c r="A22" s="67"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="60"/>
       <c r="D22" s="14"/>
-      <c r="E22" s="58"/>
+      <c r="E22" s="60"/>
       <c r="F22" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="58"/>
+      <c r="G22" s="60"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="54">
+      <c r="A23" s="68">
         <v>5</v>
       </c>
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="59"/>
+      <c r="C23" s="61"/>
       <c r="D23" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E23" s="59" t="s">
+      <c r="E23" s="61" t="s">
         <v>19</v>
       </c>
       <c r="F23" s="31" t="s">
@@ -1934,69 +1958,69 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="59"/>
+      <c r="A24" s="68"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="61"/>
       <c r="D24" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="E24" s="59"/>
+      <c r="E24" s="61"/>
       <c r="F24" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G24" s="59" t="s">
+      <c r="G24" s="61" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="54"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="59"/>
+      <c r="A25" s="68"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="61"/>
       <c r="D25" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="E25" s="59"/>
+      <c r="E25" s="61"/>
       <c r="F25" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="G25" s="59"/>
+      <c r="G25" s="61"/>
     </row>
     <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="54"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="59"/>
+      <c r="A26" s="68"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="61"/>
       <c r="D26" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E26" s="59"/>
+      <c r="E26" s="61"/>
       <c r="F26" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="G26" s="59"/>
+      <c r="G26" s="61"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="54"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="59"/>
+      <c r="A27" s="68"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="61"/>
       <c r="D27" s="15"/>
-      <c r="E27" s="59"/>
+      <c r="E27" s="61"/>
       <c r="F27" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G27" s="59"/>
+      <c r="G27" s="61"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="55">
+      <c r="A28" s="74">
         <v>6</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="60"/>
+      <c r="C28" s="62"/>
       <c r="D28" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="60" t="s">
+      <c r="E28" s="62" t="s">
         <v>20</v>
       </c>
       <c r="F28" s="34" t="s">
@@ -2007,138 +2031,138 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="55"/>
-      <c r="B29" s="55"/>
-      <c r="C29" s="60"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="62"/>
       <c r="D29" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="E29" s="60"/>
+      <c r="E29" s="62"/>
       <c r="F29" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="60" t="s">
+      <c r="G29" s="62" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="55"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="60"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="62"/>
       <c r="D30" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="E30" s="60"/>
+      <c r="E30" s="62"/>
       <c r="F30" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="G30" s="60"/>
+      <c r="G30" s="62"/>
     </row>
     <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="55"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="60"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="62"/>
       <c r="D31" s="16"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="62"/>
       <c r="F31" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="G31" s="60"/>
+      <c r="G31" s="62"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="55"/>
-      <c r="B32" s="55"/>
-      <c r="C32" s="60"/>
+      <c r="A32" s="74"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="62"/>
       <c r="D32" s="16"/>
-      <c r="E32" s="60"/>
+      <c r="E32" s="62"/>
       <c r="F32" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="60"/>
+      <c r="G32" s="62"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="56">
+      <c r="A33" s="75">
         <v>7</v>
       </c>
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="61"/>
+      <c r="C33" s="63"/>
       <c r="D33" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="E33" s="61" t="s">
+      <c r="E33" s="63" t="s">
         <v>21</v>
       </c>
       <c r="F33" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="88" t="s">
+      <c r="G33" s="55" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="56"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="61"/>
+      <c r="A34" s="75"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="63"/>
       <c r="D34" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="61"/>
+      <c r="E34" s="63"/>
       <c r="F34" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="61" t="s">
+      <c r="G34" s="63" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="61"/>
+      <c r="A35" s="75"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="63"/>
       <c r="D35" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E35" s="61"/>
+      <c r="E35" s="63"/>
       <c r="F35" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="61"/>
+      <c r="G35" s="63"/>
     </row>
     <row r="36" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="56"/>
-      <c r="B36" s="56"/>
-      <c r="C36" s="61"/>
+      <c r="A36" s="75"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="63"/>
       <c r="D36" s="17"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="87" t="s">
+      <c r="E36" s="63"/>
+      <c r="F36" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="G36" s="61"/>
+      <c r="G36" s="63"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="56"/>
-      <c r="B37" s="56"/>
-      <c r="C37" s="61"/>
+      <c r="A37" s="75"/>
+      <c r="B37" s="75"/>
+      <c r="C37" s="63"/>
       <c r="D37" s="17"/>
-      <c r="E37" s="61"/>
+      <c r="E37" s="63"/>
       <c r="F37" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G37" s="61"/>
+      <c r="G37" s="63"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="57">
+      <c r="A38" s="56">
         <v>8</v>
       </c>
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="62"/>
+      <c r="C38" s="76"/>
       <c r="D38" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E38" s="62" t="s">
+      <c r="E38" s="76" t="s">
         <v>22</v>
       </c>
       <c r="F38" s="39" t="s">
@@ -2149,82 +2173,57 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="57"/>
-      <c r="B39" s="57"/>
-      <c r="C39" s="62"/>
+      <c r="A39" s="56"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="76"/>
       <c r="D39" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E39" s="62"/>
+      <c r="E39" s="76"/>
       <c r="F39" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="G39" s="62" t="s">
+      <c r="G39" s="76" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="57"/>
-      <c r="B40" s="57"/>
-      <c r="C40" s="62"/>
+      <c r="A40" s="56"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="76"/>
       <c r="D40" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="E40" s="62"/>
+      <c r="E40" s="76"/>
       <c r="F40" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="G40" s="62"/>
+      <c r="G40" s="76"/>
     </row>
     <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="57"/>
-      <c r="B41" s="57"/>
-      <c r="C41" s="62"/>
+      <c r="A41" s="56"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="76"/>
       <c r="D41" s="18"/>
-      <c r="E41" s="62"/>
+      <c r="E41" s="76"/>
       <c r="F41" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="G41" s="62"/>
+      <c r="G41" s="76"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="57"/>
-      <c r="B42" s="57"/>
-      <c r="C42" s="62"/>
+      <c r="A42" s="56"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="76"/>
       <c r="D42" s="18"/>
-      <c r="E42" s="62"/>
+      <c r="E42" s="76"/>
       <c r="F42" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G42" s="62"/>
+      <c r="G42" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="B38:B42"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="C18:C22"/>
-    <mergeCell ref="C23:C27"/>
-    <mergeCell ref="C28:C32"/>
-    <mergeCell ref="C33:C37"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="G9:G12"/>
-    <mergeCell ref="G14:G17"/>
-    <mergeCell ref="E3:E7"/>
-    <mergeCell ref="E8:E12"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="E18:E22"/>
-    <mergeCell ref="G4:G7"/>
     <mergeCell ref="A23:A27"/>
     <mergeCell ref="A28:A32"/>
     <mergeCell ref="A33:A37"/>
@@ -2241,6 +2240,31 @@
     <mergeCell ref="E38:E42"/>
     <mergeCell ref="B28:B32"/>
     <mergeCell ref="B33:B37"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="E18:E22"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="B38:B42"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="C28:C32"/>
+    <mergeCell ref="C33:C37"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="B23:B27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2261,15 +2285,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
@@ -2281,10 +2305,10 @@
       <c r="C2" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="78"/>
+      <c r="E2" s="88"/>
       <c r="F2" s="3" t="s">
         <v>69</v>
       </c>
@@ -2293,10 +2317,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="85">
+      <c r="A3" s="77">
         <v>1</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="79" t="s">
         <v>151</v>
       </c>
       <c r="C3" s="51" t="s">
@@ -2305,47 +2329,41 @@
       <c r="D3" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="48">
-        <v>6</v>
-      </c>
+      <c r="E3" s="48"/>
       <c r="F3" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="80"/>
+      <c r="G3" s="81"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="85"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="79" t="s">
+      <c r="A4" s="77"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80" t="s">
         <v>98</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="48">
-        <v>5</v>
-      </c>
+      <c r="E4" s="48"/>
       <c r="F4" s="43"/>
-      <c r="G4" s="80"/>
+      <c r="G4" s="81"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="85"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="79"/>
+      <c r="A5" s="77"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
       <c r="D5" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="48">
-        <v>2.5</v>
-      </c>
+      <c r="E5" s="48"/>
       <c r="F5" s="43"/>
-      <c r="G5" s="80"/>
+      <c r="G5" s="81"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="85">
+      <c r="A6" s="77">
         <v>2</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="79" t="s">
         <v>150</v>
       </c>
       <c r="C6" s="52" t="s">
@@ -2354,47 +2372,41 @@
       <c r="D6" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="49">
-        <v>10</v>
-      </c>
+      <c r="E6" s="49"/>
       <c r="F6" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="80"/>
+      <c r="G6" s="81"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="85"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="79" t="s">
+      <c r="A7" s="77"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="80" t="s">
         <v>75</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="49">
-        <v>10</v>
-      </c>
+      <c r="E7" s="49"/>
       <c r="F7" s="43"/>
-      <c r="G7" s="80"/>
+      <c r="G7" s="81"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="85"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="79"/>
+      <c r="A8" s="77"/>
+      <c r="B8" s="79"/>
+      <c r="C8" s="80"/>
       <c r="D8" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="49">
-        <v>1.8</v>
-      </c>
+      <c r="E8" s="49"/>
       <c r="F8" s="43"/>
-      <c r="G8" s="80"/>
+      <c r="G8" s="81"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="85">
+      <c r="A9" s="77">
         <v>3</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="79" t="s">
         <v>73</v>
       </c>
       <c r="C9" s="53" t="s">
@@ -2407,12 +2419,12 @@
       <c r="F9" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="G9" s="80"/>
+      <c r="G9" s="81"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="85"/>
-      <c r="B10" s="81"/>
-      <c r="C10" s="79" t="s">
+      <c r="A10" s="77"/>
+      <c r="B10" s="79"/>
+      <c r="C10" s="80" t="s">
         <v>103</v>
       </c>
       <c r="D10" s="47" t="s">
@@ -2420,24 +2432,24 @@
       </c>
       <c r="E10" s="49"/>
       <c r="F10" s="43"/>
-      <c r="G10" s="80"/>
+      <c r="G10" s="81"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="85"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="79"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="80"/>
       <c r="D11" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E11" s="49"/>
       <c r="F11" s="43"/>
-      <c r="G11" s="80"/>
+      <c r="G11" s="81"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="85">
+      <c r="A12" s="77">
         <v>4</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="79" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="53" t="s">
@@ -2450,12 +2462,12 @@
       <c r="F12" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="80"/>
+      <c r="G12" s="81"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="85"/>
-      <c r="B13" s="81"/>
-      <c r="C13" s="79" t="s">
+      <c r="A13" s="77"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="80" t="s">
         <v>76</v>
       </c>
       <c r="D13" s="47" t="s">
@@ -2463,24 +2475,24 @@
       </c>
       <c r="E13" s="49"/>
       <c r="F13" s="43"/>
-      <c r="G13" s="80"/>
+      <c r="G13" s="81"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="85"/>
-      <c r="B14" s="81"/>
-      <c r="C14" s="79"/>
+      <c r="A14" s="77"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="80"/>
       <c r="D14" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="43"/>
-      <c r="G14" s="80"/>
+      <c r="G14" s="81"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="85">
+      <c r="A15" s="77">
         <v>5</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="79" t="s">
         <v>100</v>
       </c>
       <c r="C15" s="51" t="s">
@@ -2493,12 +2505,12 @@
       <c r="F15" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="G15" s="80"/>
+      <c r="G15" s="81"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="85"/>
-      <c r="B16" s="81"/>
-      <c r="C16" s="75" t="s">
+      <c r="A16" s="77"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="82" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="47" t="s">
@@ -2506,24 +2518,24 @@
       </c>
       <c r="E16" s="49"/>
       <c r="F16" s="43"/>
-      <c r="G16" s="80"/>
+      <c r="G16" s="81"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="85"/>
-      <c r="B17" s="81"/>
-      <c r="C17" s="76"/>
+      <c r="A17" s="77"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="83"/>
       <c r="D17" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E17" s="49"/>
       <c r="F17" s="43"/>
-      <c r="G17" s="80"/>
+      <c r="G17" s="81"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="85">
+      <c r="A18" s="77">
         <v>6</v>
       </c>
-      <c r="B18" s="81" t="s">
+      <c r="B18" s="79" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="51" t="s">
@@ -2536,12 +2548,12 @@
       <c r="F18" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="80"/>
+      <c r="G18" s="81"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="85"/>
-      <c r="B19" s="81"/>
-      <c r="C19" s="75" t="s">
+      <c r="A19" s="77"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="82" t="s">
         <v>99</v>
       </c>
       <c r="D19" s="47" t="s">
@@ -2549,24 +2561,24 @@
       </c>
       <c r="E19" s="49"/>
       <c r="F19" s="43"/>
-      <c r="G19" s="80"/>
+      <c r="G19" s="81"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="85"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="76"/>
+      <c r="A20" s="77"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="83"/>
       <c r="D20" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E20" s="49"/>
       <c r="F20" s="43"/>
-      <c r="G20" s="80"/>
+      <c r="G20" s="81"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="85">
+      <c r="A21" s="77">
         <v>7</v>
       </c>
-      <c r="B21" s="81" t="s">
+      <c r="B21" s="79" t="s">
         <v>152</v>
       </c>
       <c r="C21" s="51" t="s">
@@ -2579,12 +2591,12 @@
       <c r="F21" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="80"/>
+      <c r="G21" s="81"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="85"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="75" t="s">
+      <c r="A22" s="77"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="82" t="s">
         <v>99</v>
       </c>
       <c r="D22" s="47" t="s">
@@ -2594,24 +2606,24 @@
       <c r="F22" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="G22" s="80"/>
+      <c r="G22" s="81"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
-      <c r="B23" s="81"/>
-      <c r="C23" s="76"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="83"/>
       <c r="D23" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E23" s="49"/>
       <c r="F23" s="43"/>
-      <c r="G23" s="80"/>
+      <c r="G23" s="81"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="85">
+      <c r="A24" s="77">
         <v>8</v>
       </c>
-      <c r="B24" s="81" t="s">
+      <c r="B24" s="79" t="s">
         <v>101</v>
       </c>
       <c r="C24" s="51" t="s">
@@ -2624,12 +2636,12 @@
       <c r="F24" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="G24" s="80"/>
+      <c r="G24" s="81"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="75" t="s">
+      <c r="A25" s="77"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="82" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="47" t="s">
@@ -2639,24 +2651,24 @@
       <c r="F25" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="G25" s="80"/>
+      <c r="G25" s="81"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="76"/>
+      <c r="A26" s="77"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="83"/>
       <c r="D26" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E26" s="49"/>
       <c r="F26" s="43"/>
-      <c r="G26" s="80"/>
+      <c r="G26" s="81"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="85">
+      <c r="A27" s="77">
         <v>9</v>
       </c>
-      <c r="B27" s="81" t="s">
+      <c r="B27" s="79" t="s">
         <v>105</v>
       </c>
       <c r="C27" s="51" t="s">
@@ -2669,12 +2681,12 @@
       <c r="F27" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="G27" s="80"/>
+      <c r="G27" s="81"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="75" t="s">
+      <c r="A28" s="77"/>
+      <c r="B28" s="79"/>
+      <c r="C28" s="82" t="s">
         <v>99</v>
       </c>
       <c r="D28" s="47" t="s">
@@ -2682,24 +2694,24 @@
       </c>
       <c r="E28" s="49"/>
       <c r="F28" s="43"/>
-      <c r="G28" s="80"/>
+      <c r="G28" s="81"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="76"/>
+      <c r="A29" s="77"/>
+      <c r="B29" s="79"/>
+      <c r="C29" s="83"/>
       <c r="D29" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E29" s="49"/>
       <c r="F29" s="43"/>
-      <c r="G29" s="80"/>
+      <c r="G29" s="81"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="85">
+      <c r="A30" s="77">
         <v>10</v>
       </c>
-      <c r="B30" s="82" t="s">
+      <c r="B30" s="84" t="s">
         <v>153</v>
       </c>
       <c r="C30" s="51" t="s">
@@ -2712,12 +2724,12 @@
       <c r="F30" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="G30" s="80"/>
+      <c r="G30" s="81"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
-      <c r="B31" s="83"/>
-      <c r="C31" s="75" t="s">
+      <c r="A31" s="77"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="82" t="s">
         <v>99</v>
       </c>
       <c r="D31" s="47" t="s">
@@ -2727,24 +2739,24 @@
       <c r="F31" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="G31" s="80"/>
+      <c r="G31" s="81"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="84"/>
-      <c r="C32" s="76"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="83"/>
       <c r="D32" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E32" s="49"/>
       <c r="F32" s="43"/>
-      <c r="G32" s="80"/>
+      <c r="G32" s="81"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="85">
+      <c r="A33" s="77">
         <v>11</v>
       </c>
-      <c r="B33" s="81" t="s">
+      <c r="B33" s="79" t="s">
         <v>154</v>
       </c>
       <c r="C33" s="51" t="s">
@@ -2757,12 +2769,12 @@
       <c r="F33" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="G33" s="80"/>
+      <c r="G33" s="81"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="81"/>
-      <c r="C34" s="75" t="s">
+      <c r="A34" s="77"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="82" t="s">
         <v>99</v>
       </c>
       <c r="D34" s="47" t="s">
@@ -2770,24 +2782,24 @@
       </c>
       <c r="E34" s="49"/>
       <c r="F34" s="43"/>
-      <c r="G34" s="80"/>
+      <c r="G34" s="81"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="85"/>
-      <c r="B35" s="81"/>
-      <c r="C35" s="76"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="83"/>
       <c r="D35" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E35" s="49"/>
       <c r="F35" s="43"/>
-      <c r="G35" s="80"/>
+      <c r="G35" s="81"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="85">
+      <c r="A36" s="77">
         <v>12</v>
       </c>
-      <c r="B36" s="81" t="s">
+      <c r="B36" s="79" t="s">
         <v>108</v>
       </c>
       <c r="C36" s="51" t="s">
@@ -2800,12 +2812,12 @@
       <c r="F36" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="G36" s="80"/>
+      <c r="G36" s="81"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
-      <c r="B37" s="81"/>
-      <c r="C37" s="75" t="s">
+      <c r="A37" s="77"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="82" t="s">
         <v>107</v>
       </c>
       <c r="D37" s="47" t="s">
@@ -2815,24 +2827,24 @@
       <c r="F37" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="G37" s="80"/>
+      <c r="G37" s="81"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="85"/>
-      <c r="B38" s="81"/>
-      <c r="C38" s="76"/>
+      <c r="A38" s="77"/>
+      <c r="B38" s="79"/>
+      <c r="C38" s="83"/>
       <c r="D38" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E38" s="49"/>
       <c r="F38" s="43"/>
-      <c r="G38" s="80"/>
+      <c r="G38" s="81"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="85">
+      <c r="A39" s="77">
         <v>13</v>
       </c>
-      <c r="B39" s="81" t="s">
+      <c r="B39" s="79" t="s">
         <v>102</v>
       </c>
       <c r="C39" s="51" t="s">
@@ -2845,12 +2857,12 @@
       <c r="F39" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="G39" s="80"/>
+      <c r="G39" s="81"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
-      <c r="B40" s="81"/>
-      <c r="C40" s="75" t="s">
+      <c r="A40" s="77"/>
+      <c r="B40" s="79"/>
+      <c r="C40" s="82" t="s">
         <v>107</v>
       </c>
       <c r="D40" s="47" t="s">
@@ -2860,24 +2872,24 @@
       <c r="F40" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G40" s="80"/>
+      <c r="G40" s="81"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
-      <c r="B41" s="81"/>
-      <c r="C41" s="76"/>
+      <c r="A41" s="77"/>
+      <c r="B41" s="79"/>
+      <c r="C41" s="83"/>
       <c r="D41" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E41" s="49"/>
       <c r="F41" s="43"/>
-      <c r="G41" s="80"/>
+      <c r="G41" s="81"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="85">
+      <c r="A42" s="77">
         <v>14</v>
       </c>
-      <c r="B42" s="81" t="s">
+      <c r="B42" s="79" t="s">
         <v>92</v>
       </c>
       <c r="C42" s="51" t="s">
@@ -2890,12 +2902,12 @@
       <c r="F42" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="G42" s="80"/>
+      <c r="G42" s="81"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="85"/>
-      <c r="B43" s="81"/>
-      <c r="C43" s="75" t="s">
+      <c r="A43" s="77"/>
+      <c r="B43" s="79"/>
+      <c r="C43" s="82" t="s">
         <v>93</v>
       </c>
       <c r="D43" s="47" t="s">
@@ -2905,12 +2917,12 @@
       <c r="F43" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="G43" s="80"/>
+      <c r="G43" s="81"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="85"/>
-      <c r="B44" s="81"/>
-      <c r="C44" s="76"/>
+      <c r="A44" s="77"/>
+      <c r="B44" s="79"/>
+      <c r="C44" s="83"/>
       <c r="D44" s="47" t="s">
         <v>81</v>
       </c>
@@ -2918,13 +2930,13 @@
       <c r="F44" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="G44" s="80"/>
+      <c r="G44" s="81"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="85">
+      <c r="A45" s="77">
         <v>15</v>
       </c>
-      <c r="B45" s="81" t="s">
+      <c r="B45" s="79" t="s">
         <v>91</v>
       </c>
       <c r="C45" s="51" t="s">
@@ -2937,12 +2949,12 @@
       <c r="F45" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="G45" s="80"/>
+      <c r="G45" s="81"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="85"/>
-      <c r="B46" s="81"/>
-      <c r="C46" s="75" t="s">
+      <c r="A46" s="77"/>
+      <c r="B46" s="79"/>
+      <c r="C46" s="82" t="s">
         <v>93</v>
       </c>
       <c r="D46" s="47" t="s">
@@ -2950,24 +2962,24 @@
       </c>
       <c r="E46" s="49"/>
       <c r="F46" s="43"/>
-      <c r="G46" s="80"/>
+      <c r="G46" s="81"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="85"/>
-      <c r="B47" s="81"/>
-      <c r="C47" s="76"/>
+      <c r="A47" s="77"/>
+      <c r="B47" s="79"/>
+      <c r="C47" s="83"/>
       <c r="D47" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E47" s="49"/>
       <c r="F47" s="43"/>
-      <c r="G47" s="80"/>
+      <c r="G47" s="81"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="85">
+      <c r="A48" s="77">
         <v>16</v>
       </c>
-      <c r="B48" s="81" t="s">
+      <c r="B48" s="79" t="s">
         <v>90</v>
       </c>
       <c r="C48" s="51" t="s">
@@ -2980,12 +2992,12 @@
       <c r="F48" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="G48" s="80"/>
+      <c r="G48" s="81"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="85"/>
-      <c r="B49" s="81"/>
-      <c r="C49" s="75" t="s">
+      <c r="A49" s="77"/>
+      <c r="B49" s="79"/>
+      <c r="C49" s="82" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="47" t="s">
@@ -2997,24 +3009,24 @@
       <c r="F49" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="G49" s="80"/>
+      <c r="G49" s="81"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="85"/>
-      <c r="B50" s="81"/>
-      <c r="C50" s="76"/>
+      <c r="A50" s="77"/>
+      <c r="B50" s="79"/>
+      <c r="C50" s="83"/>
       <c r="D50" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E50" s="49"/>
       <c r="F50" s="43"/>
-      <c r="G50" s="80"/>
+      <c r="G50" s="81"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="85">
+      <c r="A51" s="77">
         <v>17</v>
       </c>
-      <c r="B51" s="81" t="s">
+      <c r="B51" s="79" t="s">
         <v>89</v>
       </c>
       <c r="C51" s="51" t="s">
@@ -3027,12 +3039,12 @@
       <c r="F51" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="G51" s="80"/>
+      <c r="G51" s="81"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="85"/>
-      <c r="B52" s="81"/>
-      <c r="C52" s="75" t="s">
+      <c r="A52" s="77"/>
+      <c r="B52" s="79"/>
+      <c r="C52" s="82" t="s">
         <v>93</v>
       </c>
       <c r="D52" s="47" t="s">
@@ -3040,24 +3052,24 @@
       </c>
       <c r="E52" s="49"/>
       <c r="F52" s="43"/>
-      <c r="G52" s="80"/>
+      <c r="G52" s="81"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="85"/>
-      <c r="B53" s="81"/>
-      <c r="C53" s="76"/>
+      <c r="A53" s="77"/>
+      <c r="B53" s="79"/>
+      <c r="C53" s="83"/>
       <c r="D53" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E53" s="49"/>
       <c r="F53" s="43"/>
-      <c r="G53" s="80"/>
+      <c r="G53" s="81"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="85">
+      <c r="A54" s="77">
         <v>18</v>
       </c>
-      <c r="B54" s="81" t="s">
+      <c r="B54" s="79" t="s">
         <v>88</v>
       </c>
       <c r="C54" s="51" t="s">
@@ -3070,12 +3082,12 @@
       <c r="F54" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="G54" s="80"/>
+      <c r="G54" s="81"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="85"/>
-      <c r="B55" s="81"/>
-      <c r="C55" s="75" t="s">
+      <c r="A55" s="77"/>
+      <c r="B55" s="79"/>
+      <c r="C55" s="82" t="s">
         <v>93</v>
       </c>
       <c r="D55" s="47" t="s">
@@ -3085,21 +3097,79 @@
       <c r="F55" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="G55" s="80"/>
+      <c r="G55" s="81"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="85"/>
-      <c r="B56" s="81"/>
-      <c r="C56" s="76"/>
+      <c r="A56" s="77"/>
+      <c r="B56" s="79"/>
+      <c r="C56" s="83"/>
       <c r="D56" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E56" s="49"/>
       <c r="F56" s="43"/>
-      <c r="G56" s="80"/>
+      <c r="G56" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A51:A53"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:A5"/>
@@ -3116,64 +3186,6 @@
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B18:B20"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="G48:G50"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="G54:G56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C28:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3181,9 +3193,58 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E03245DE-3A38-45B1-AED2-B529B7A0614F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="89" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="89" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Диздок (GDD)/Баланс.xlsx
+++ b/Диздок (GDD)/Баланс.xlsx
@@ -8,26 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Working folder of Dima\Projects\Gearspell Tower\Диздок (GDD)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F76BE42-4ED7-4812-A6F7-C351C6C11F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C951438-CD57-4971-B7A1-3603DCD628BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Снаряжение" sheetId="1" r:id="rId1"/>
     <sheet name="Враги" sheetId="2" r:id="rId2"/>
-    <sheet name="Баланс" sheetId="3" r:id="rId3"/>
+    <sheet name="Баланс волн" sheetId="3" r:id="rId3"/>
+    <sheet name="Значения" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="186">
   <si>
     <t>Название</t>
   </si>
@@ -783,13 +793,82 @@
     <t>Mage</t>
   </si>
   <si>
-    <t>Fire_Elemental</t>
-  </si>
-  <si>
-    <t>Spider_Golem</t>
-  </si>
-  <si>
-    <t>Drop (ev)</t>
+    <t>Состав</t>
+  </si>
+  <si>
+    <t>Σ Дроп</t>
+  </si>
+  <si>
+    <t>Награда</t>
+  </si>
+  <si>
+    <t>20F</t>
+  </si>
+  <si>
+    <t>Итого:</t>
+  </si>
+  <si>
+    <t>Враг</t>
+  </si>
+  <si>
+    <t>Дроп (ср)</t>
+  </si>
+  <si>
+    <t>мин</t>
+  </si>
+  <si>
+    <t>макс</t>
+  </si>
+  <si>
+    <t>Fire elemental</t>
+  </si>
+  <si>
+    <t>Spider Golem</t>
+  </si>
+  <si>
+    <t>Слот</t>
+  </si>
+  <si>
+    <t>Ценна</t>
+  </si>
+  <si>
+    <t>Рюкзак</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Common (х2)</t>
+  </si>
+  <si>
+    <t>Fork</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>5F</t>
+  </si>
+  <si>
+    <t>16F+6D</t>
+  </si>
+  <si>
+    <t>18F+6D+2M</t>
+  </si>
+  <si>
+    <t>12F+4D+7M</t>
+  </si>
+  <si>
+    <t>2M+8F+4M+1G</t>
+  </si>
+  <si>
+    <t>2D+16F+6D+8M+2G</t>
+  </si>
+  <si>
+    <t>За волну</t>
+  </si>
+  <si>
+    <t>Σ Итого</t>
   </si>
 </sst>
 </file>
@@ -799,7 +878,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -887,6 +966,21 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -956,7 +1050,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1051,11 +1145,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1212,106 +1371,141 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1613,15 +1807,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="70"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
@@ -1647,17 +1841,17 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="64">
+      <c r="A3" s="77">
         <v>1</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="57"/>
+      <c r="C3" s="86"/>
       <c r="D3" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="83" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -1668,67 +1862,67 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="57"/>
+      <c r="A4" s="77"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="86"/>
       <c r="D4" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="73"/>
+      <c r="E4" s="83"/>
       <c r="F4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="57" t="s">
+      <c r="G4" s="86" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64"/>
-      <c r="C5" s="57"/>
+      <c r="A5" s="77"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="86"/>
       <c r="D5" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E5" s="73"/>
+      <c r="E5" s="83"/>
       <c r="F5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="57"/>
+      <c r="G5" s="86"/>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="64"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="57"/>
+      <c r="A6" s="77"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="86"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="73"/>
+      <c r="E6" s="83"/>
       <c r="F6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="57"/>
+      <c r="G6" s="86"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="64"/>
-      <c r="B7" s="64"/>
-      <c r="C7" s="57"/>
+      <c r="A7" s="77"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="86"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="73"/>
+      <c r="E7" s="83"/>
       <c r="F7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="57"/>
+      <c r="G7" s="86"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="65">
+      <c r="A8" s="78">
         <v>2</v>
       </c>
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="58"/>
+      <c r="C8" s="84"/>
       <c r="D8" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="58" t="s">
+      <c r="E8" s="84" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="10" t="s">
@@ -1739,69 +1933,69 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="65"/>
-      <c r="B9" s="65"/>
-      <c r="C9" s="58"/>
+      <c r="A9" s="78"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="84"/>
       <c r="D9" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="58"/>
+      <c r="E9" s="84"/>
       <c r="F9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="71" t="s">
+      <c r="G9" s="81" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="65"/>
-      <c r="B10" s="65"/>
-      <c r="C10" s="58"/>
+      <c r="A10" s="78"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="84"/>
       <c r="D10" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="58"/>
+      <c r="E10" s="84"/>
       <c r="F10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="71"/>
+      <c r="G10" s="81"/>
     </row>
     <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="65"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="58"/>
+      <c r="A11" s="78"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="84"/>
       <c r="D11" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="58"/>
+      <c r="E11" s="84"/>
       <c r="F11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="71"/>
+      <c r="G11" s="81"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="65"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="58"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="84"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="58"/>
+      <c r="E12" s="84"/>
       <c r="F12" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="71"/>
+      <c r="G12" s="81"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="66">
+      <c r="A13" s="79">
         <v>3</v>
       </c>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="59"/>
+      <c r="C13" s="85"/>
       <c r="D13" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="59" t="s">
+      <c r="E13" s="85" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="24" t="s">
@@ -1812,69 +2006,69 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="66"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="59"/>
+      <c r="A14" s="79"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="85"/>
       <c r="D14" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E14" s="59"/>
+      <c r="E14" s="85"/>
       <c r="F14" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="72" t="s">
+      <c r="G14" s="82" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="66"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="59"/>
+      <c r="A15" s="79"/>
+      <c r="B15" s="79"/>
+      <c r="C15" s="85"/>
       <c r="D15" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E15" s="59"/>
+      <c r="E15" s="85"/>
       <c r="F15" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="72"/>
+      <c r="G15" s="82"/>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="66"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="59"/>
+      <c r="A16" s="79"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="85"/>
       <c r="D16" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E16" s="59"/>
+      <c r="E16" s="85"/>
       <c r="F16" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="72"/>
+      <c r="G16" s="82"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="66"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="59"/>
+      <c r="A17" s="79"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="85"/>
       <c r="D17" s="13"/>
-      <c r="E17" s="59"/>
+      <c r="E17" s="85"/>
       <c r="F17" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G17" s="72"/>
+      <c r="G17" s="82"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="67">
+      <c r="A18" s="80">
         <v>4</v>
       </c>
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="60"/>
+      <c r="C18" s="70"/>
       <c r="D18" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E18" s="60" t="s">
+      <c r="E18" s="70" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="28" t="s">
@@ -1885,69 +2079,69 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="67"/>
-      <c r="B19" s="67"/>
-      <c r="C19" s="60"/>
+      <c r="A19" s="80"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="70"/>
       <c r="D19" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E19" s="60"/>
+      <c r="E19" s="70"/>
       <c r="F19" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="60" t="s">
+      <c r="G19" s="70" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="67"/>
-      <c r="B20" s="67"/>
-      <c r="C20" s="60"/>
+      <c r="A20" s="80"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="70"/>
       <c r="D20" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E20" s="60"/>
+      <c r="E20" s="70"/>
       <c r="F20" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="G20" s="60"/>
+      <c r="G20" s="70"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="67"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="60"/>
+      <c r="A21" s="80"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="70"/>
       <c r="D21" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E21" s="60"/>
+      <c r="E21" s="70"/>
       <c r="F21" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="60"/>
+      <c r="G21" s="70"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="67"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="60"/>
+      <c r="A22" s="80"/>
+      <c r="B22" s="80"/>
+      <c r="C22" s="70"/>
       <c r="D22" s="14"/>
-      <c r="E22" s="60"/>
+      <c r="E22" s="70"/>
       <c r="F22" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="60"/>
+      <c r="G22" s="70"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="68">
+      <c r="A23" s="66">
         <v>5</v>
       </c>
-      <c r="B23" s="68" t="s">
+      <c r="B23" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="61"/>
+      <c r="C23" s="71"/>
       <c r="D23" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E23" s="61" t="s">
+      <c r="E23" s="71" t="s">
         <v>19</v>
       </c>
       <c r="F23" s="31" t="s">
@@ -1958,69 +2152,69 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="68"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="61"/>
+      <c r="A24" s="66"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="71"/>
       <c r="D24" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="E24" s="61"/>
+      <c r="E24" s="71"/>
       <c r="F24" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G24" s="61" t="s">
+      <c r="G24" s="71" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="68"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="61"/>
+      <c r="A25" s="66"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="71"/>
       <c r="D25" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="E25" s="61"/>
+      <c r="E25" s="71"/>
       <c r="F25" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="G25" s="61"/>
+      <c r="G25" s="71"/>
     </row>
     <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="68"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="61"/>
+      <c r="A26" s="66"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="71"/>
       <c r="D26" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E26" s="61"/>
+      <c r="E26" s="71"/>
       <c r="F26" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="G26" s="61"/>
+      <c r="G26" s="71"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="68"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="61"/>
+      <c r="A27" s="66"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="71"/>
       <c r="D27" s="15"/>
-      <c r="E27" s="61"/>
+      <c r="E27" s="71"/>
       <c r="F27" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G27" s="61"/>
+      <c r="G27" s="71"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="74">
+      <c r="A28" s="67">
         <v>6</v>
       </c>
-      <c r="B28" s="74" t="s">
+      <c r="B28" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="62"/>
+      <c r="C28" s="72"/>
       <c r="D28" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="62" t="s">
+      <c r="E28" s="72" t="s">
         <v>20</v>
       </c>
       <c r="F28" s="34" t="s">
@@ -2031,67 +2225,67 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="74"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="62"/>
+      <c r="A29" s="67"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="72"/>
       <c r="D29" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="E29" s="62"/>
+      <c r="E29" s="72"/>
       <c r="F29" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="62" t="s">
+      <c r="G29" s="72" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="74"/>
-      <c r="B30" s="74"/>
-      <c r="C30" s="62"/>
+      <c r="A30" s="67"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="72"/>
       <c r="D30" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="E30" s="62"/>
+      <c r="E30" s="72"/>
       <c r="F30" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="G30" s="62"/>
+      <c r="G30" s="72"/>
     </row>
     <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="74"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="62"/>
+      <c r="A31" s="67"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="72"/>
       <c r="D31" s="16"/>
-      <c r="E31" s="62"/>
+      <c r="E31" s="72"/>
       <c r="F31" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="G31" s="62"/>
+      <c r="G31" s="72"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="74"/>
-      <c r="B32" s="74"/>
-      <c r="C32" s="62"/>
+      <c r="A32" s="67"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="72"/>
       <c r="D32" s="16"/>
-      <c r="E32" s="62"/>
+      <c r="E32" s="72"/>
       <c r="F32" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="62"/>
+      <c r="G32" s="72"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="75">
+      <c r="A33" s="68">
         <v>7</v>
       </c>
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="63"/>
+      <c r="C33" s="73"/>
       <c r="D33" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="E33" s="63" t="s">
+      <c r="E33" s="73" t="s">
         <v>21</v>
       </c>
       <c r="F33" s="37" t="s">
@@ -2102,67 +2296,67 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="75"/>
-      <c r="B34" s="75"/>
-      <c r="C34" s="63"/>
+      <c r="A34" s="68"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="73"/>
       <c r="D34" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="63"/>
+      <c r="E34" s="73"/>
       <c r="F34" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="63" t="s">
+      <c r="G34" s="73" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
-      <c r="B35" s="75"/>
-      <c r="C35" s="63"/>
+      <c r="A35" s="68"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="73"/>
       <c r="D35" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E35" s="63"/>
+      <c r="E35" s="73"/>
       <c r="F35" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="63"/>
+      <c r="G35" s="73"/>
     </row>
     <row r="36" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="75"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="63"/>
+      <c r="A36" s="68"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="73"/>
       <c r="D36" s="17"/>
-      <c r="E36" s="63"/>
+      <c r="E36" s="73"/>
       <c r="F36" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="G36" s="63"/>
+      <c r="G36" s="73"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="75"/>
-      <c r="B37" s="75"/>
-      <c r="C37" s="63"/>
+      <c r="A37" s="68"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="73"/>
       <c r="D37" s="17"/>
-      <c r="E37" s="63"/>
+      <c r="E37" s="73"/>
       <c r="F37" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G37" s="63"/>
+      <c r="G37" s="73"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="56">
+      <c r="A38" s="69">
         <v>8</v>
       </c>
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="76"/>
+      <c r="C38" s="74"/>
       <c r="D38" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E38" s="76" t="s">
+      <c r="E38" s="74" t="s">
         <v>22</v>
       </c>
       <c r="F38" s="39" t="s">
@@ -2173,57 +2367,82 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="56"/>
-      <c r="B39" s="56"/>
-      <c r="C39" s="76"/>
+      <c r="A39" s="69"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="74"/>
       <c r="D39" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E39" s="76"/>
+      <c r="E39" s="74"/>
       <c r="F39" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="G39" s="76" t="s">
+      <c r="G39" s="74" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="56"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="76"/>
+      <c r="A40" s="69"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="74"/>
       <c r="D40" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="E40" s="76"/>
+      <c r="E40" s="74"/>
       <c r="F40" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="G40" s="76"/>
+      <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="56"/>
-      <c r="B41" s="56"/>
-      <c r="C41" s="76"/>
+      <c r="A41" s="69"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="74"/>
       <c r="D41" s="18"/>
-      <c r="E41" s="76"/>
+      <c r="E41" s="74"/>
       <c r="F41" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="G41" s="76"/>
+      <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="56"/>
-      <c r="B42" s="56"/>
-      <c r="C42" s="76"/>
+      <c r="A42" s="69"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="74"/>
       <c r="D42" s="18"/>
-      <c r="E42" s="76"/>
+      <c r="E42" s="74"/>
       <c r="F42" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G42" s="76"/>
+      <c r="G42" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="B38:B42"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="C28:C32"/>
+    <mergeCell ref="C33:C37"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="E18:E22"/>
+    <mergeCell ref="G4:G7"/>
     <mergeCell ref="A23:A27"/>
     <mergeCell ref="A28:A32"/>
     <mergeCell ref="A33:A37"/>
@@ -2240,31 +2459,6 @@
     <mergeCell ref="E38:E42"/>
     <mergeCell ref="B28:B32"/>
     <mergeCell ref="B33:B37"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="G9:G12"/>
-    <mergeCell ref="G14:G17"/>
-    <mergeCell ref="E3:E7"/>
-    <mergeCell ref="E8:E12"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="E18:E22"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="B38:B42"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="C18:C22"/>
-    <mergeCell ref="C23:C27"/>
-    <mergeCell ref="C28:C32"/>
-    <mergeCell ref="C33:C37"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="B23:B27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2285,15 +2479,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
@@ -2305,10 +2499,10 @@
       <c r="C2" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="87" t="s">
+      <c r="D2" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="88"/>
+      <c r="E2" s="90"/>
       <c r="F2" s="3" t="s">
         <v>69</v>
       </c>
@@ -2317,10 +2511,10 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="77">
+      <c r="A3" s="94">
         <v>1</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="93" t="s">
         <v>151</v>
       </c>
       <c r="C3" s="51" t="s">
@@ -2333,12 +2527,12 @@
       <c r="F3" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="81"/>
+      <c r="G3" s="92"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="77"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="80" t="s">
+      <c r="A4" s="94"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="91" t="s">
         <v>98</v>
       </c>
       <c r="D4" s="47" t="s">
@@ -2346,24 +2540,24 @@
       </c>
       <c r="E4" s="48"/>
       <c r="F4" s="43"/>
-      <c r="G4" s="81"/>
+      <c r="G4" s="92"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="77"/>
-      <c r="B5" s="79"/>
-      <c r="C5" s="80"/>
+      <c r="A5" s="94"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="91"/>
       <c r="D5" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E5" s="48"/>
       <c r="F5" s="43"/>
-      <c r="G5" s="81"/>
+      <c r="G5" s="92"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="77">
+      <c r="A6" s="94">
         <v>2</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="93" t="s">
         <v>150</v>
       </c>
       <c r="C6" s="52" t="s">
@@ -2376,12 +2570,12 @@
       <c r="F6" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="81"/>
+      <c r="G6" s="92"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="77"/>
-      <c r="B7" s="79"/>
-      <c r="C7" s="80" t="s">
+      <c r="A7" s="94"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="91" t="s">
         <v>75</v>
       </c>
       <c r="D7" s="47" t="s">
@@ -2389,24 +2583,24 @@
       </c>
       <c r="E7" s="49"/>
       <c r="F7" s="43"/>
-      <c r="G7" s="81"/>
+      <c r="G7" s="92"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="77"/>
-      <c r="B8" s="79"/>
-      <c r="C8" s="80"/>
+      <c r="A8" s="94"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="91"/>
       <c r="D8" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E8" s="49"/>
       <c r="F8" s="43"/>
-      <c r="G8" s="81"/>
+      <c r="G8" s="92"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="77">
+      <c r="A9" s="94">
         <v>3</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="93" t="s">
         <v>73</v>
       </c>
       <c r="C9" s="53" t="s">
@@ -2419,12 +2613,12 @@
       <c r="F9" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="G9" s="81"/>
+      <c r="G9" s="92"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="77"/>
-      <c r="B10" s="79"/>
-      <c r="C10" s="80" t="s">
+      <c r="A10" s="94"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="91" t="s">
         <v>103</v>
       </c>
       <c r="D10" s="47" t="s">
@@ -2432,24 +2626,24 @@
       </c>
       <c r="E10" s="49"/>
       <c r="F10" s="43"/>
-      <c r="G10" s="81"/>
+      <c r="G10" s="92"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="77"/>
-      <c r="B11" s="79"/>
-      <c r="C11" s="80"/>
+      <c r="A11" s="94"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="91"/>
       <c r="D11" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E11" s="49"/>
       <c r="F11" s="43"/>
-      <c r="G11" s="81"/>
+      <c r="G11" s="92"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="77">
+      <c r="A12" s="94">
         <v>4</v>
       </c>
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="93" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="53" t="s">
@@ -2462,12 +2656,12 @@
       <c r="F12" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="81"/>
+      <c r="G12" s="92"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="77"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="80" t="s">
+      <c r="A13" s="94"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="91" t="s">
         <v>76</v>
       </c>
       <c r="D13" s="47" t="s">
@@ -2475,24 +2669,24 @@
       </c>
       <c r="E13" s="49"/>
       <c r="F13" s="43"/>
-      <c r="G13" s="81"/>
+      <c r="G13" s="92"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="77"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="80"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="91"/>
       <c r="D14" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E14" s="49"/>
       <c r="F14" s="43"/>
-      <c r="G14" s="81"/>
+      <c r="G14" s="92"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="77">
+      <c r="A15" s="94">
         <v>5</v>
       </c>
-      <c r="B15" s="79" t="s">
+      <c r="B15" s="93" t="s">
         <v>100</v>
       </c>
       <c r="C15" s="51" t="s">
@@ -2505,12 +2699,12 @@
       <c r="F15" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="G15" s="81"/>
+      <c r="G15" s="92"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="77"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="82" t="s">
+      <c r="A16" s="94"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="87" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="47" t="s">
@@ -2518,24 +2712,24 @@
       </c>
       <c r="E16" s="49"/>
       <c r="F16" s="43"/>
-      <c r="G16" s="81"/>
+      <c r="G16" s="92"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="77"/>
-      <c r="B17" s="79"/>
-      <c r="C17" s="83"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="88"/>
       <c r="D17" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E17" s="49"/>
       <c r="F17" s="43"/>
-      <c r="G17" s="81"/>
+      <c r="G17" s="92"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="77">
+      <c r="A18" s="94">
         <v>6</v>
       </c>
-      <c r="B18" s="79" t="s">
+      <c r="B18" s="93" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="51" t="s">
@@ -2548,12 +2742,12 @@
       <c r="F18" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="81"/>
+      <c r="G18" s="92"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="77"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="82" t="s">
+      <c r="A19" s="94"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="87" t="s">
         <v>99</v>
       </c>
       <c r="D19" s="47" t="s">
@@ -2561,24 +2755,24 @@
       </c>
       <c r="E19" s="49"/>
       <c r="F19" s="43"/>
-      <c r="G19" s="81"/>
+      <c r="G19" s="92"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="77"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="83"/>
+      <c r="A20" s="94"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="88"/>
       <c r="D20" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E20" s="49"/>
       <c r="F20" s="43"/>
-      <c r="G20" s="81"/>
+      <c r="G20" s="92"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="77">
+      <c r="A21" s="94">
         <v>7</v>
       </c>
-      <c r="B21" s="79" t="s">
+      <c r="B21" s="93" t="s">
         <v>152</v>
       </c>
       <c r="C21" s="51" t="s">
@@ -2591,12 +2785,12 @@
       <c r="F21" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="81"/>
+      <c r="G21" s="92"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="77"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="82" t="s">
+      <c r="A22" s="94"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="87" t="s">
         <v>99</v>
       </c>
       <c r="D22" s="47" t="s">
@@ -2606,24 +2800,24 @@
       <c r="F22" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="G22" s="81"/>
+      <c r="G22" s="92"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="77"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="83"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="88"/>
       <c r="D23" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E23" s="49"/>
       <c r="F23" s="43"/>
-      <c r="G23" s="81"/>
+      <c r="G23" s="92"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="77">
+      <c r="A24" s="94">
         <v>8</v>
       </c>
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="93" t="s">
         <v>101</v>
       </c>
       <c r="C24" s="51" t="s">
@@ -2636,12 +2830,12 @@
       <c r="F24" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="G24" s="81"/>
+      <c r="G24" s="92"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="77"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="82" t="s">
+      <c r="A25" s="94"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="87" t="s">
         <v>99</v>
       </c>
       <c r="D25" s="47" t="s">
@@ -2651,24 +2845,24 @@
       <c r="F25" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="G25" s="81"/>
+      <c r="G25" s="92"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="77"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="83"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="88"/>
       <c r="D26" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E26" s="49"/>
       <c r="F26" s="43"/>
-      <c r="G26" s="81"/>
+      <c r="G26" s="92"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="77">
+      <c r="A27" s="94">
         <v>9</v>
       </c>
-      <c r="B27" s="79" t="s">
+      <c r="B27" s="93" t="s">
         <v>105</v>
       </c>
       <c r="C27" s="51" t="s">
@@ -2681,12 +2875,12 @@
       <c r="F27" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="G27" s="81"/>
+      <c r="G27" s="92"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="77"/>
-      <c r="B28" s="79"/>
-      <c r="C28" s="82" t="s">
+      <c r="A28" s="94"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="87" t="s">
         <v>99</v>
       </c>
       <c r="D28" s="47" t="s">
@@ -2694,24 +2888,24 @@
       </c>
       <c r="E28" s="49"/>
       <c r="F28" s="43"/>
-      <c r="G28" s="81"/>
+      <c r="G28" s="92"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="77"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="83"/>
+      <c r="A29" s="94"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="88"/>
       <c r="D29" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E29" s="49"/>
       <c r="F29" s="43"/>
-      <c r="G29" s="81"/>
+      <c r="G29" s="92"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="77">
+      <c r="A30" s="94">
         <v>10</v>
       </c>
-      <c r="B30" s="84" t="s">
+      <c r="B30" s="95" t="s">
         <v>153</v>
       </c>
       <c r="C30" s="51" t="s">
@@ -2724,12 +2918,12 @@
       <c r="F30" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="G30" s="81"/>
+      <c r="G30" s="92"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="77"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="82" t="s">
+      <c r="A31" s="94"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="87" t="s">
         <v>99</v>
       </c>
       <c r="D31" s="47" t="s">
@@ -2739,24 +2933,24 @@
       <c r="F31" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="G31" s="81"/>
+      <c r="G31" s="92"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="77"/>
-      <c r="B32" s="86"/>
-      <c r="C32" s="83"/>
+      <c r="A32" s="94"/>
+      <c r="B32" s="97"/>
+      <c r="C32" s="88"/>
       <c r="D32" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E32" s="49"/>
       <c r="F32" s="43"/>
-      <c r="G32" s="81"/>
+      <c r="G32" s="92"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="77">
+      <c r="A33" s="94">
         <v>11</v>
       </c>
-      <c r="B33" s="79" t="s">
+      <c r="B33" s="93" t="s">
         <v>154</v>
       </c>
       <c r="C33" s="51" t="s">
@@ -2769,12 +2963,12 @@
       <c r="F33" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="G33" s="81"/>
+      <c r="G33" s="92"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="77"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="82" t="s">
+      <c r="A34" s="94"/>
+      <c r="B34" s="93"/>
+      <c r="C34" s="87" t="s">
         <v>99</v>
       </c>
       <c r="D34" s="47" t="s">
@@ -2782,24 +2976,24 @@
       </c>
       <c r="E34" s="49"/>
       <c r="F34" s="43"/>
-      <c r="G34" s="81"/>
+      <c r="G34" s="92"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="77"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="83"/>
+      <c r="A35" s="94"/>
+      <c r="B35" s="93"/>
+      <c r="C35" s="88"/>
       <c r="D35" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E35" s="49"/>
       <c r="F35" s="43"/>
-      <c r="G35" s="81"/>
+      <c r="G35" s="92"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="77">
+      <c r="A36" s="94">
         <v>12</v>
       </c>
-      <c r="B36" s="79" t="s">
+      <c r="B36" s="93" t="s">
         <v>108</v>
       </c>
       <c r="C36" s="51" t="s">
@@ -2812,12 +3006,12 @@
       <c r="F36" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="G36" s="81"/>
+      <c r="G36" s="92"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="77"/>
-      <c r="B37" s="79"/>
-      <c r="C37" s="82" t="s">
+      <c r="A37" s="94"/>
+      <c r="B37" s="93"/>
+      <c r="C37" s="87" t="s">
         <v>107</v>
       </c>
       <c r="D37" s="47" t="s">
@@ -2827,24 +3021,24 @@
       <c r="F37" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="G37" s="81"/>
+      <c r="G37" s="92"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="77"/>
-      <c r="B38" s="79"/>
-      <c r="C38" s="83"/>
+      <c r="A38" s="94"/>
+      <c r="B38" s="93"/>
+      <c r="C38" s="88"/>
       <c r="D38" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E38" s="49"/>
       <c r="F38" s="43"/>
-      <c r="G38" s="81"/>
+      <c r="G38" s="92"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="77">
+      <c r="A39" s="94">
         <v>13</v>
       </c>
-      <c r="B39" s="79" t="s">
+      <c r="B39" s="93" t="s">
         <v>102</v>
       </c>
       <c r="C39" s="51" t="s">
@@ -2857,12 +3051,12 @@
       <c r="F39" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="G39" s="81"/>
+      <c r="G39" s="92"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="77"/>
-      <c r="B40" s="79"/>
-      <c r="C40" s="82" t="s">
+      <c r="A40" s="94"/>
+      <c r="B40" s="93"/>
+      <c r="C40" s="87" t="s">
         <v>107</v>
       </c>
       <c r="D40" s="47" t="s">
@@ -2872,24 +3066,24 @@
       <c r="F40" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="G40" s="81"/>
+      <c r="G40" s="92"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="77"/>
-      <c r="B41" s="79"/>
-      <c r="C41" s="83"/>
+      <c r="A41" s="94"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="88"/>
       <c r="D41" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E41" s="49"/>
       <c r="F41" s="43"/>
-      <c r="G41" s="81"/>
+      <c r="G41" s="92"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="77">
+      <c r="A42" s="94">
         <v>14</v>
       </c>
-      <c r="B42" s="79" t="s">
+      <c r="B42" s="93" t="s">
         <v>92</v>
       </c>
       <c r="C42" s="51" t="s">
@@ -2902,12 +3096,12 @@
       <c r="F42" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="G42" s="81"/>
+      <c r="G42" s="92"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="77"/>
-      <c r="B43" s="79"/>
-      <c r="C43" s="82" t="s">
+      <c r="A43" s="94"/>
+      <c r="B43" s="93"/>
+      <c r="C43" s="87" t="s">
         <v>93</v>
       </c>
       <c r="D43" s="47" t="s">
@@ -2917,12 +3111,12 @@
       <c r="F43" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="G43" s="81"/>
+      <c r="G43" s="92"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="77"/>
-      <c r="B44" s="79"/>
-      <c r="C44" s="83"/>
+      <c r="A44" s="94"/>
+      <c r="B44" s="93"/>
+      <c r="C44" s="88"/>
       <c r="D44" s="47" t="s">
         <v>81</v>
       </c>
@@ -2930,13 +3124,13 @@
       <c r="F44" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="G44" s="81"/>
+      <c r="G44" s="92"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="77">
+      <c r="A45" s="94">
         <v>15</v>
       </c>
-      <c r="B45" s="79" t="s">
+      <c r="B45" s="93" t="s">
         <v>91</v>
       </c>
       <c r="C45" s="51" t="s">
@@ -2949,12 +3143,12 @@
       <c r="F45" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="G45" s="81"/>
+      <c r="G45" s="92"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="77"/>
-      <c r="B46" s="79"/>
-      <c r="C46" s="82" t="s">
+      <c r="A46" s="94"/>
+      <c r="B46" s="93"/>
+      <c r="C46" s="87" t="s">
         <v>93</v>
       </c>
       <c r="D46" s="47" t="s">
@@ -2962,24 +3156,24 @@
       </c>
       <c r="E46" s="49"/>
       <c r="F46" s="43"/>
-      <c r="G46" s="81"/>
+      <c r="G46" s="92"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="77"/>
-      <c r="B47" s="79"/>
-      <c r="C47" s="83"/>
+      <c r="A47" s="94"/>
+      <c r="B47" s="93"/>
+      <c r="C47" s="88"/>
       <c r="D47" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E47" s="49"/>
       <c r="F47" s="43"/>
-      <c r="G47" s="81"/>
+      <c r="G47" s="92"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="77">
+      <c r="A48" s="94">
         <v>16</v>
       </c>
-      <c r="B48" s="79" t="s">
+      <c r="B48" s="93" t="s">
         <v>90</v>
       </c>
       <c r="C48" s="51" t="s">
@@ -2992,12 +3186,12 @@
       <c r="F48" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="G48" s="81"/>
+      <c r="G48" s="92"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="77"/>
-      <c r="B49" s="79"/>
-      <c r="C49" s="82" t="s">
+      <c r="A49" s="94"/>
+      <c r="B49" s="93"/>
+      <c r="C49" s="87" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="47" t="s">
@@ -3009,24 +3203,24 @@
       <c r="F49" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="G49" s="81"/>
+      <c r="G49" s="92"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="77"/>
-      <c r="B50" s="79"/>
-      <c r="C50" s="83"/>
+      <c r="A50" s="94"/>
+      <c r="B50" s="93"/>
+      <c r="C50" s="88"/>
       <c r="D50" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E50" s="49"/>
       <c r="F50" s="43"/>
-      <c r="G50" s="81"/>
+      <c r="G50" s="92"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="77">
+      <c r="A51" s="94">
         <v>17</v>
       </c>
-      <c r="B51" s="79" t="s">
+      <c r="B51" s="93" t="s">
         <v>89</v>
       </c>
       <c r="C51" s="51" t="s">
@@ -3039,12 +3233,12 @@
       <c r="F51" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="G51" s="81"/>
+      <c r="G51" s="92"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="77"/>
-      <c r="B52" s="79"/>
-      <c r="C52" s="82" t="s">
+      <c r="A52" s="94"/>
+      <c r="B52" s="93"/>
+      <c r="C52" s="87" t="s">
         <v>93</v>
       </c>
       <c r="D52" s="47" t="s">
@@ -3052,24 +3246,24 @@
       </c>
       <c r="E52" s="49"/>
       <c r="F52" s="43"/>
-      <c r="G52" s="81"/>
+      <c r="G52" s="92"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="77"/>
-      <c r="B53" s="79"/>
-      <c r="C53" s="83"/>
+      <c r="A53" s="94"/>
+      <c r="B53" s="93"/>
+      <c r="C53" s="88"/>
       <c r="D53" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E53" s="49"/>
       <c r="F53" s="43"/>
-      <c r="G53" s="81"/>
+      <c r="G53" s="92"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="77">
+      <c r="A54" s="94">
         <v>18</v>
       </c>
-      <c r="B54" s="79" t="s">
+      <c r="B54" s="93" t="s">
         <v>88</v>
       </c>
       <c r="C54" s="51" t="s">
@@ -3082,12 +3276,12 @@
       <c r="F54" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="G54" s="81"/>
+      <c r="G54" s="92"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="77"/>
-      <c r="B55" s="79"/>
-      <c r="C55" s="82" t="s">
+      <c r="A55" s="94"/>
+      <c r="B55" s="93"/>
+      <c r="C55" s="87" t="s">
         <v>93</v>
       </c>
       <c r="D55" s="47" t="s">
@@ -3097,21 +3291,79 @@
       <c r="F55" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="G55" s="81"/>
+      <c r="G55" s="92"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="77"/>
-      <c r="B56" s="79"/>
-      <c r="C56" s="83"/>
+      <c r="A56" s="94"/>
+      <c r="B56" s="93"/>
+      <c r="C56" s="88"/>
       <c r="D56" s="47" t="s">
         <v>81</v>
       </c>
       <c r="E56" s="49"/>
       <c r="F56" s="43"/>
-      <c r="G56" s="81"/>
+      <c r="G56" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="G54:G56"/>
     <mergeCell ref="C55:C56"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="C37:C38"/>
@@ -3128,64 +3380,6 @@
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="G48:G50"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="G54:G56"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3193,58 +3387,409 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E03245DE-3A38-45B1-AED2-B529B7A0614F}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" s="57" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="58">
+        <v>1</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="59">
+        <f>5*Значения!C2</f>
+        <v>20</v>
+      </c>
+      <c r="D2" s="59">
+        <v>0</v>
+      </c>
+      <c r="E2" s="59">
+        <f>SUM(C2:D2)</f>
+        <v>20</v>
+      </c>
+      <c r="F2" s="57">
+        <f>E2</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="58">
+        <v>2</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="59">
+        <f>20*Значения!C2</f>
+        <v>80</v>
+      </c>
+      <c r="D3" s="59">
+        <v>15</v>
+      </c>
+      <c r="E3" s="59">
+        <f t="shared" ref="E3:E8" si="0">SUM(C3:D3)</f>
+        <v>95</v>
+      </c>
+      <c r="F3" s="57">
+        <f>E3+F2</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="58">
+        <v>3</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="59">
+        <f>15*Значения!C2+6*Значения!C3</f>
+        <v>96</v>
+      </c>
+      <c r="D4" s="59">
+        <v>25</v>
+      </c>
+      <c r="E4" s="59">
+        <f t="shared" si="0"/>
+        <v>121</v>
+      </c>
+      <c r="F4" s="57">
+        <f t="shared" ref="F4:F8" si="1">E4+F3</f>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="58">
+        <v>4</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="59">
+        <f>18*Значения!C2+6*Значения!C3+2*Значения!C4</f>
+        <v>148</v>
+      </c>
+      <c r="D5" s="59">
+        <v>35</v>
+      </c>
+      <c r="E5" s="59">
+        <f t="shared" si="0"/>
+        <v>183</v>
+      </c>
+      <c r="F5" s="57">
+        <f t="shared" si="1"/>
+        <v>419</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="58">
+        <v>5</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="59">
+        <f>12*Значения!C2+4*Значения!C3+7*Значения!C4</f>
+        <v>212</v>
+      </c>
+      <c r="D6" s="59">
+        <v>45</v>
+      </c>
+      <c r="E6" s="59">
+        <f t="shared" si="0"/>
+        <v>257</v>
+      </c>
+      <c r="F6" s="57">
+        <f t="shared" si="1"/>
+        <v>676</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="58">
         <v>6</v>
       </c>
-      <c r="B1" s="89" t="s">
-        <v>162</v>
-      </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B5">
-        <v>28</v>
+      <c r="B7" s="59" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="59">
+        <f>8*Значения!C2+0*Значения!C3+6*Значения!C4+1*Значения!C5</f>
+        <v>192</v>
+      </c>
+      <c r="D7" s="59">
+        <v>55</v>
+      </c>
+      <c r="E7" s="59">
+        <f t="shared" si="0"/>
+        <v>247</v>
+      </c>
+      <c r="F7" s="57">
+        <f t="shared" si="1"/>
+        <v>923</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="58">
+        <v>7</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="59">
+        <f>16*Значения!C2+8*Значения!C3+8*Значения!C4+2*Значения!C5</f>
+        <v>352</v>
+      </c>
+      <c r="D8" s="59">
+        <v>65</v>
+      </c>
+      <c r="E8" s="59">
+        <f t="shared" si="0"/>
+        <v>417</v>
+      </c>
+      <c r="F8" s="57">
+        <f t="shared" si="1"/>
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="99" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="100"/>
+      <c r="C9" s="59">
+        <f>SUM(C2:C8)</f>
+        <v>1100</v>
+      </c>
+      <c r="D9" s="59">
+        <f>SUM(D2:D8)</f>
+        <v>240</v>
+      </c>
+      <c r="E9" s="59">
+        <f>SUM(E2:E8)</f>
+        <v>1340</v>
+      </c>
+      <c r="F9" s="57">
+        <f>F8</f>
+        <v>1340</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:B9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C40EEED-B211-414F-86E7-C41E260D78D5}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
+    <col min="10" max="10" width="21.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="62" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1" s="63" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="62" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="58">
+        <v>1</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="59">
+        <f>AVERAGE(D2:E2)</f>
+        <v>4</v>
+      </c>
+      <c r="D2" s="59">
+        <v>2</v>
+      </c>
+      <c r="E2" s="59">
+        <v>6</v>
+      </c>
+      <c r="G2" s="60">
+        <v>1</v>
+      </c>
+      <c r="H2" s="59">
+        <v>0</v>
+      </c>
+      <c r="J2" s="62" t="s">
+        <v>174</v>
+      </c>
+      <c r="K2" s="61">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="58">
+        <v>2</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="59">
+        <f t="shared" ref="C3:C5" si="0">AVERAGE(D3:E3)</f>
+        <v>6</v>
+      </c>
+      <c r="D3" s="59">
+        <v>3</v>
+      </c>
+      <c r="E3" s="59">
+        <v>9</v>
+      </c>
+      <c r="G3" s="58">
+        <v>2</v>
+      </c>
+      <c r="H3" s="59">
+        <v>50</v>
+      </c>
+      <c r="J3" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="K3" s="59">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="58">
+        <v>3</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="59">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D4" s="59">
+        <v>10</v>
+      </c>
+      <c r="E4" s="59">
+        <v>30</v>
+      </c>
+      <c r="G4" s="58">
+        <v>3</v>
+      </c>
+      <c r="H4" s="59">
+        <v>300</v>
+      </c>
+      <c r="J4" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="K4" s="59">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="58">
+        <v>4</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="59">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="D5" s="59">
+        <v>30</v>
+      </c>
+      <c r="E5" s="59">
+        <v>50</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="H5" s="64">
+        <v>0</v>
+      </c>
+      <c r="J5" s="65" t="s">
+        <v>177</v>
+      </c>
+      <c r="K5" s="59">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G6" s="65" t="s">
+        <v>164</v>
+      </c>
+      <c r="H6" s="59">
+        <f>SUM(H2:H5)</f>
+        <v>350</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>164</v>
+      </c>
+      <c r="K6" s="59">
+        <f>SUM(K2:K5)</f>
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>